--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/NEVADA_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/NEVADA_2010.xlsx
@@ -2436,7 +2436,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C116">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C164">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C195">
@@ -22164,7 +22164,7 @@
       </c>
       <c r="B1212" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1212">
